--- a/agent/新岛Forge服务器Mod列表-修订版.xlsx
+++ b/agent/新岛Forge服务器Mod列表-修订版.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模组清单" sheetId="1" r:id="R8089c1c55453463c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模组清单" sheetId="1" r:id="R6fd978ca32974965"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -195,7 +195,7 @@
         <x:color rgb="FF6C3434"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4D8D8"/>
         </x:patternFill>
       </x:fill>
@@ -205,7 +205,7 @@
         <x:color rgb="FF6F571D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0C7"/>
         </x:patternFill>
       </x:fill>
@@ -215,7 +215,7 @@
         <x:color rgb="FF805B18"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0C7"/>
         </x:patternFill>
       </x:fill>
@@ -225,7 +225,7 @@
         <x:color rgb="FF805B18"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0C7"/>
         </x:patternFill>
       </x:fill>
@@ -235,7 +235,7 @@
         <x:color rgb="FF805B18"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0C7"/>
         </x:patternFill>
       </x:fill>
@@ -489,7 +489,7 @@
         <x:v>备注（v1.6 更新）</x:v>
       </x:c>
       <x:c r="K1" s="14" t="str">
-        <x:v>当前 index 文件（2026-10-04）</x:v>
+        <x:v>当前 index 文件</x:v>
       </x:c>
       <x:c r="L1" s="14" t="str">
         <x:v>index / 原表状态</x:v>
@@ -4511,7 +4511,7 @@
         <x:v>保留原表划除状态；v1.6 测试备注仍待处理。</x:v>
       </x:c>
     </x:row>
-    <x:row r="131" ht="30" customHeight="1">
+    <x:row r="131" ht="42.75" customHeight="1">
       <x:c r="A131" s="4" t="str">
         <x:v>Curios API</x:v>
       </x:c>
@@ -4533,16 +4533,21 @@
       </x:c>
       <x:c r="H131" s="4"/>
       <x:c r="I131" s="4"/>
-      <x:c r="J131" s="4"/>
+      <x:c r="J131" s="4" t="str">
+        <x:v>2026-10-05 新增 5.14.1+1.20.1；已入 index，待游戏测试。</x:v>
+      </x:c>
       <x:c r="K131" s="4" t="str">
-        <x:v>—</x:v>
+        <x:v>curios-forge-5.14.1+1.20.1.jar</x:v>
       </x:c>
       <x:c r="L131" s="4" t="str">
-        <x:v>待确认入包；index 未收录</x:v>
-      </x:c>
-      <x:c r="M131" s="24"/>
-    </x:row>
-    <x:row r="132" ht="30" customHeight="1">
+        <x:v>已入索引，待测试</x:v>
+      </x:c>
+      <x:c r="M131" s="24" t="str">
+        <x:v>官方 Forge 1.20.1 正式版。
+https://modrinth.com/mod/curios/version/IPQlZkz1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="42.75" customHeight="1">
       <x:c r="A132" s="5" t="str">
         <x:v>Caelus API</x:v>
       </x:c>
@@ -4564,16 +4569,21 @@
       </x:c>
       <x:c r="H132" s="5"/>
       <x:c r="I132" s="5"/>
-      <x:c r="J132" s="5"/>
+      <x:c r="J132" s="5" t="str">
+        <x:v>2026-10-05 新增 3.2.0+1.20.1；已入 index，待游戏测试。</x:v>
+      </x:c>
       <x:c r="K132" s="5" t="str">
-        <x:v>—</x:v>
+        <x:v>caelus-forge-3.2.0+1.20.1.jar</x:v>
       </x:c>
       <x:c r="L132" s="5" t="str">
-        <x:v>待确认入包；index 未收录</x:v>
-      </x:c>
-      <x:c r="M132" s="23"/>
-    </x:row>
-    <x:row r="133" ht="30" customHeight="1">
+        <x:v>已入索引，待测试</x:v>
+      </x:c>
+      <x:c r="M132" s="23" t="str">
+        <x:v>官方 Forge 1.20.1 正式版。
+https://modrinth.com/mod/caelus/version/mRry0DgY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="42.75" customHeight="1">
       <x:c r="A133" s="4" t="str">
         <x:v>Elytra Slot</x:v>
       </x:c>
@@ -4584,10 +4594,10 @@
         <x:v>6.4.4</x:v>
       </x:c>
       <x:c r="D133" s="4" t="str">
-        <x:v>待确认：Curios API；Caelus API</x:v>
+        <x:v>Curios API；Caelus API</x:v>
       </x:c>
       <x:c r="E133" s="4" t="str">
-        <x:v>使鞘翅和喷气背包可以同时装备</x:v>
+        <x:v>鞘翅饰品槽位；与胸甲/喷气背包搭配待实测</x:v>
       </x:c>
       <x:c r="F133" s="17" t="str">
         <x:v>需装</x:v>
@@ -4597,15 +4607,18 @@
       </x:c>
       <x:c r="H133" s="4"/>
       <x:c r="I133" s="4"/>
-      <x:c r="J133" s="4"/>
+      <x:c r="J133" s="4" t="str">
+        <x:v>2026-10-05 新增 6.4.4+1.20.1；已入 index，待游戏测试。</x:v>
+      </x:c>
       <x:c r="K133" s="4" t="str">
-        <x:v>—</x:v>
+        <x:v>elytraslot-forge-6.4.4+1.20.1.jar</x:v>
       </x:c>
       <x:c r="L133" s="4" t="str">
-        <x:v>待确认入包；index 未收录</x:v>
+        <x:v>已入索引，待测试</x:v>
       </x:c>
       <x:c r="M133" s="24" t="str">
-        <x:v>原“-2, -1”按相对位置恢复为候选名称，未验证。</x:v>
+        <x:v>官方 Forge 1.20.1 正式版。
+https://modrinth.com/mod/elytra-slot/version/k6lA080t</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="9.75" customHeight="1">

--- a/agent/新岛Forge服务器Mod列表-修订版.xlsx
+++ b/agent/新岛Forge服务器Mod列表-修订版.xlsx
@@ -1428,7 +1428,7 @@
       </x:c>
       <x:c r="M32" s="23"/>
     </x:row>
-    <x:row r="33" ht="42.75" customHeight="1">
+    <x:row r="33" ht="190" customHeight="1">
       <x:c r="A33" s="4" t="str">
         <x:v>One Enough Item</x:v>
       </x:c>
@@ -1453,15 +1453,21 @@
         <x:v>更新至 1.0.6（新前置：One Enough Lib）</x:v>
       </x:c>
       <x:c r="J33" s="4"/>
-      <x:c r="K33" s="4" t="str">
-        <x:v>OneEnoughItem-1.0.6.jar</x:v>
+      <x:c r="K33" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【过时】OneEnoughItem-1.0.6.jar</x:t>
+        </x:is>
       </x:c>
       <x:c r="L33" s="4" t="str">
         <x:v>已收录</x:v>
       </x:c>
-      <x:c r="M33" s="24" t="str">
-        <x:v>按 v1.5 备注补齐 One Enough Lib；当前 index 仍保留该库。
-历史备注中的前置编号 101 改为名称。</x:v>
+      <x:c r="M33" s="24" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【过时备注，保留原文】
+按 v1.5 备注补齐 One Enough Lib；当前 index 仍保留该库。
+历史备注中的前置编号 101 改为名称。
+状态更新（2026-10-09）：包及两服现用 OneEnoughItem-Forge-1.0.5.1.jar；已移除独立 OELib 0.0.5。依据：40e7866及当前索引。</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="34" ht="30" customHeight="1">
@@ -3591,7 +3597,7 @@
       <x:c r="L100" s="7"/>
       <x:c r="M100" s="25"/>
     </x:row>
-    <x:row r="101" ht="30" customHeight="1">
+    <x:row r="101" ht="155" customHeight="1">
       <x:c r="A101" s="4" t="str">
         <x:v>One Enough Lib</x:v>
       </x:c>
@@ -3613,17 +3619,27 @@
       </x:c>
       <x:c r="H101" s="4"/>
       <x:c r="I101" s="4"/>
-      <x:c r="J101" s="4" t="str">
-        <x:v>历史提议（未落实）：删除此前置并降级 OEI</x:v>
-      </x:c>
-      <x:c r="K101" s="4" t="str">
-        <x:v>OELib-forge-0.0.5.jar</x:v>
-      </x:c>
-      <x:c r="L101" s="4" t="str">
-        <x:v>已收录</x:v>
-      </x:c>
-      <x:c r="M101" s="24" t="str">
-        <x:v>当前 index 为 OEI 1.0.6 + OELib 0.0.5，此备注不代表已执行。</x:v>
+      <x:c r="J101" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【过时】历史提议（未落实）：删除此前置并降级 OEI</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K101" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【过时】OELib-forge-0.0.5.jar</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L101" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已收录（过时）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M101" s="24" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【过时备注，保留原文】
+当前 index 为 OEI 1.0.6 + OELib 0.0.5，此备注不代表已执行。
+状态更新（2026-10-09）：OEI 回退与独立 OELib 移除已落实；OEI 仍含内嵌库。未确认游戏验收或远端部署。依据：40e7866及当前索引。</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="102" ht="24" customHeight="1">
